--- a/04_DESIGN_TABLES/DesignTable_0403_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0403_SW2.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-08-08 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-08-08</t>
+          <t>BUILD 2026-09-25: OMi 0403-08-08 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-08-08 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.81~0.813; D2@BORE=0.504~0.504; D@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-04-04 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-04-04</t>
+          <t>BUILD 2026-09-25: OMi 0403-04-04 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-04-04 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.5~0.50; D2@BORE=0.254~0.254; D@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-06-06 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-06-06</t>
+          <t>BUILD 2026-09-25: OMi 0403-06-06 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-06-06 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.63~0.625; D2@BORE=0.379~0.379; D@BORE=0.3~0.297</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-10-10 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-10-10</t>
+          <t>BUILD 2026-09-25: OMi 0403-10-10 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-10-10 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on CHEX@HEX=0.94~0.938; D2@BORE=0.631~0.631; D@BORE=0.48~0.484</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="C7" t="n">
         <v>0.79674</v>
@@ -1210,7 +1210,7 @@
         <v>0.84</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34 | MODEL: OMi 0403 (plated) parts built from the Air-Way UNPL (unplated) rows of the same size - plating does not change the shape (user decision 2026-09-25, closes QA #123); Air-Way-only UNPL sizes are no longer built; JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); braze socket = plain bore D2 to depth L7 (Air-Way); bore D from the socket bottom to the JIC tip; hex spans socket face to JIC relief</t>
+          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34; L3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L59 = 1.320 (table had 1.33) [user 2026-10-18 A19] | MODEL: OMi 0403 (plated) parts built from the Air-Way UNPL (unplated) rows of the same size - plating does not change the shape (user decision 2026-09-25, closes QA #123); Air-Way-only UNPL sizes are no longer built; JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); braze socket = plain bore D2 to depth L7 (Air-Way); bore D from the socket bottom to the JIC tip; hex spans socket face to JIC relief</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16</t>
+          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16 | A19 (user 2026-10-18, group 3 open): L3@DRIVE 1.33 -&gt; OMi 1.320 (Items!L59, M016)</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_0403_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0403_SW2.xlsx
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="C7" t="n">
         <v>0.79674</v>
@@ -1210,7 +1210,7 @@
         <v>0.84</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34; L3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L59 = 1.320 (table had 1.33) [user 2026-10-18 A19] | MODEL: OMi 0403 (plated) parts built from the Air-Way UNPL (unplated) rows of the same size - plating does not change the shape (user decision 2026-09-25, closes QA #123); Air-Way-only UNPL sizes are no longer built; JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); braze socket = plain bore D2 to depth L7 (Air-Way); bore D from the socket bottom to the JIC tip; hex spans socket face to JIC relief</t>
+          <t>Air-Way s49 only (double-pass 34 rows); Air-Way part numbers carry " UNPL" / " PF UNPL" suffixes (unplated / PF variant) kept verbatim; config names 0403-...; L7 and D2 printed to 3 decimals as on page; pass2 stated ROWS=35, both enumerate 34; L3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L59 = 1.320 (table had 1.33) [user 2026-10-18 A19]; L3@DRIVE: Air-Way 1.33 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: OMi 0403 (plated) parts built from the Air-Way UNPL (unplated) rows of the same size - plating does not change the shape (user decision 2026-09-25, closes QA #123); Air-Way-only UNPL sizes are no longer built; JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); braze socket = plain bore D2 to depth L7 (Air-Way); bore D from the socket bottom to the JIC tip; hex spans socket face to JIC relief</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16 | A19 (user 2026-10-18, group 3 open): L3@DRIVE 1.33 -&gt; OMi 1.320 (Items!L59, M016)</t>
+          <t>BUILD 2026-09-25: OMi 0403-16-16 (plated) built from this unplated Air-Way row - plating does not change the shape (user decision 2026-09-25); replaces the placeholder row 0403-16-16 | A19 (user 2026-10-18, group 3 open): L3@DRIVE 1.33 -&gt; OMi 1.320 (Items!L59, M016) | 2026-10-20 Air-Way first: L3@DRIVE OMi/Brennan 1.32 -&gt; Air-Way 1.33</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
